--- a/survey_templates/043_financial_series_interest_survey--survey_templates.xlsx
+++ b/survey_templates/043_financial_series_interest_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1158,8 +1158,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1_label'}</t>
+          <t>option_1_label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'option_1', 'label': 'option_1_label'}</t>
+          <t>option 1 label</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2_label'}</t>
+          <t>option_2_label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'option_2', 'label': 'option_2_label'}</t>
+          <t>option 2 label</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3',_'label':_'option_3_label'}</t>
+          <t>option_3_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'option_3', 'label': 'option_3_label'}</t>
+          <t>option 3 label</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_10_1',_'label':_'option_10_1_label'}</t>
+          <t>option_10_1_label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'option_10_1', 'label': 'option_10_1_label'}</t>
+          <t>option 10 1 label</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_10_2',_'label':_'option_10_2_label'}</t>
+          <t>option_10_2_label</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'option_10_2', 'label': 'option_10_2_label'}</t>
+          <t>option 10 2 label</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_15_1',_'label':_'option_15_1_label'}</t>
+          <t>option_15_1_label</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'option_15_1', 'label': 'option_15_1_label'}</t>
+          <t>option 15 1 label</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_15_2',_'label':_'option_15_2_label'}</t>
+          <t>option_15_2_label</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'option_15_2', 'label': 'option_15_2_label'}</t>
+          <t>option 15 2 label</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option_21_1',_'label':_'option_21_1_label'}</t>
+          <t>option_21_1_label</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'option_21_1', 'label': 'option_21_1_label'}</t>
+          <t>option 21 1 label</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option_21_2',_'label':_'option_21_2_label'}</t>
+          <t>option_21_2_label</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'option_21_2', 'label': 'option_21_2_label'}</t>
+          <t>option 21 2 label</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_25_1',_'label':_'option_25_1_label'}</t>
+          <t>option_25_1_label</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'option_25_1', 'label': 'option_25_1_label'}</t>
+          <t>option 25 1 label</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option_25_2',_'label':_'option_25_2_label'}</t>
+          <t>option_25_2_label</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'option_25_2', 'label': 'option_25_2_label'}</t>
+          <t>option 25 2 label</t>
         </is>
       </c>
     </row>
